--- a/entertainment_forms/005_toy_survey--entertainment_forms.xlsx
+++ b/entertainment_forms/005_toy_survey--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,53 +538,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>visit_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>How often do you visit the toy store?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>preferred_toy_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Which type of toy would you like to buy?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>toy_rating</t>
+          <t>How much do you like the current toy design?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>toy_comments</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>toy_comments</t>
+          <t>Would you recommend this toy?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>toy_recommendations</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>toy_recommendations</t>
+          <t>What is your age range?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>toy_recommendations_other</t>
+          <t>toy_related_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>toy_recommendations_other</t>
+          <t>Do you have any toy-related comments or feedback?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>toy_likert_scale</t>
+          <t>play_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>toy_likert_scale</t>
+          <t>How often do you play with toys?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,86 +699,86 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>toy_likert_scale_other</t>
+          <t>gift_toy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>toy_likert_scale_other</t>
+          <t>What kind of toy do you like to give as a gift?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>toy_likert_scale_comments</t>
+          <t>quality_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>toy_likert_scale_comments</t>
+          <t>Can you rate your satisfaction with the toy's quality?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>survey_completion</t>
+          <t>price_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>survey_completion</t>
+          <t>Can you rate your satisfaction with the toy's price?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale</t>
+          <t>Can you provide any additional comments or suggestions?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale_comments</t>
+          <t>toy_type_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale_comments</t>
+          <t>Do you have any comments about the toy's type?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale_other</t>
+          <t>toy_type_other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>toy_survey_likert_scale_other</t>
+          <t>What other types of toys would you like to see?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>toy_survey_comments</t>
+          <t>toy_rating_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>toy_survey_comments</t>
+          <t>Can you rate your satisfaction with the toy's rating?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>toy_recommendations_other</t>
+          <t>toy_rating_other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>toy_recommendations_other</t>
+          <t>What other rating would you like to see?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>toy_likert_scale_other</t>
+          <t>toy_price_comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>toy_likert_scale_other</t>
+          <t>Can you provide any comments about the toy's price?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>toy_likert_scale_comments</t>
+          <t>toy_price_other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>toy_likert_scale_comments</t>
+          <t>What other price would you like to see?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>toy_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>toy_other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>toy_comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>toy_comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>toy_survey_likert_scale_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>toy_survey_likert_scale_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>toy_survey_likert_scale_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>toy_survey_likert_scale_other</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>toy_likert_scale_comments_other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>toy_likert_scale_comments_other</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>toy_likert_scale_other_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>toy_likert_scale_other_other</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>toy_survey_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>toy_survey_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +965,544 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>toy_recommendations_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>toy_recommendations_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>toy_recommendations_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>toy_likert_scale_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>toy_likert_scale_choices</t>
+          <t>preferred_toy_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>toys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Toys</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>toy_likert_scale_choices</t>
+          <t>preferred_toy_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>games</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Games</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>preferred_toy_type_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>puzzles</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Puzzles</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>preferred_toy_type_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>electronics</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>toy_rating_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>very_much</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Very Much</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>toy_rating_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>toy_rating_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Somewhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>toy_rating_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>age_range_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>31-40</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>31-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>play_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>play_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>several_times_a_week</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Several times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>play_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>play_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gift_toy_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>toys</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Toys</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gift_toy_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gift_toy_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>puzzles</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Puzzles</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gift_toy_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>electronics</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>quality_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>quality_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>quality_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>quality_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>price_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>price_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>price_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>price_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
